--- a/data/genome_sets/GS-Zhang2025_genome_list.xlsx
+++ b/data/genome_sets/GS-Zhang2025_genome_list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_rechecked_precise_red/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/linweili/Important_files/课题进展/Nature_submission_0803/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA85C618-F4CE-7142-8BDE-300434485347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512E88F7-2662-1D49-8AD6-B63C3CC68011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="640" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4228,7 +4228,7 @@
     <t>unclassified</t>
   </si>
   <si>
-    <t>Supplementary Table 1 | Genome accessions and GTDB taxonomic classification of archaeal and eukaryotic genomes in dataset GS-Zhang2025</t>
+    <t>Supplementary Table 2 | Genome accessions and GTDB taxonomic classification of archaeal and eukaryotic genomes in dataset GS-Zhang2025</t>
   </si>
 </sst>
 </file>
